--- a/tests/browser/fixtures/pdc/maestro-sinco-mini.xlsx
+++ b/tests/browser/fixtures/pdc/maestro-sinco-mini.xlsx
@@ -56,16 +56,16 @@
     <t>AIA</t>
   </si>
   <si>
-    <t>TEST-101</t>
-  </si>
-  <si>
-    <t>PISO CERAMICO 30X30</t>
+    <t>ZZTEST-901</t>
+  </si>
+  <si>
+    <t>ZZTEST PISO CERAMICO 30X30</t>
   </si>
   <si>
     <t>03</t>
   </si>
   <si>
-    <t>MAT-ACABADOS</t>
+    <t>ZZTEST MAT-ACABADOS</t>
   </si>
   <si>
     <t>M</t>
@@ -83,22 +83,22 @@
     <t>ACTIVO</t>
   </si>
   <si>
-    <t>TEST-102</t>
-  </si>
-  <si>
-    <t>PISO PORCELANATO 60X60</t>
-  </si>
-  <si>
-    <t>TEST-103</t>
-  </si>
-  <si>
-    <t>ACERO DE REFUERZO 60000PSI</t>
+    <t>ZZTEST-902</t>
+  </si>
+  <si>
+    <t>ZZTEST PISO PORCELANATO 60X60</t>
+  </si>
+  <si>
+    <t>ZZTEST-903</t>
+  </si>
+  <si>
+    <t>ZZTEST ACERO DE REFUERZO 60000PSI</t>
   </si>
   <si>
     <t>05</t>
   </si>
   <si>
-    <t>MAT-ACEROS</t>
+    <t>ZZTEST MAT-ACEROS</t>
   </si>
   <si>
     <t>KG</t>
@@ -107,13 +107,13 @@
     <t>KILO</t>
   </si>
   <si>
-    <t>TEST-104</t>
-  </si>
-  <si>
-    <t>AYUDANTE DE OBRA</t>
-  </si>
-  <si>
-    <t>SUBCONTRATACION</t>
+    <t>ZZTEST-904</t>
+  </si>
+  <si>
+    <t>ZZTEST AYUDANTE DE OBRA</t>
+  </si>
+  <si>
+    <t>ZZTEST SUBCONTRATACION</t>
   </si>
   <si>
     <t>S</t>
@@ -128,13 +128,13 @@
     <t>HORA</t>
   </si>
   <si>
-    <t>TEST-105</t>
-  </si>
-  <si>
-    <t>ALQUILER ANDAMIO</t>
-  </si>
-  <si>
-    <t>ALQUILER MAQUINARIA</t>
+    <t>ZZTEST-905</t>
+  </si>
+  <si>
+    <t>ZZTEST ALQUILER ANDAMIO</t>
+  </si>
+  <si>
+    <t>ZZTEST ALQUILER MAQUINARIA</t>
   </si>
   <si>
     <t>E</t>
@@ -146,13 +146,13 @@
     <t>DIA</t>
   </si>
   <si>
-    <t>TEST-106</t>
-  </si>
-  <si>
-    <t>INSUMO OBSOLETO</t>
-  </si>
-  <si>
-    <t>OTROS</t>
+    <t>ZZTEST-906</t>
+  </si>
+  <si>
+    <t>ZZTEST INSUMO OBSOLETO</t>
+  </si>
+  <si>
+    <t>ZZTEST OTROS</t>
   </si>
   <si>
     <t>UN</t>
